--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486836_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486836_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4462</v>
+        <v>5.6655</v>
       </c>
       <c r="E2" t="n">
-        <v>3.77</v>
+        <v>3.4115</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6761</v>
+        <v>2.254</v>
       </c>
       <c r="G2" t="n">
         <v>3.6088</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7875</v>
+        <v>1.0068</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1302</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6573</v>
+        <v>0.2351</v>
       </c>
       <c r="V2" t="n">
         <v>0.8568</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1228</v>
+        <v>3.4511</v>
       </c>
       <c r="E3" t="n">
-        <v>4.441</v>
+        <v>4.4962</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3182</v>
+        <v>-1.045</v>
       </c>
       <c r="G3" t="n">
         <v>5.8099</v>
@@ -688,13 +688,13 @@
         <v>0.5792</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8109</v>
+        <v>-0.4826</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4139</v>
+        <v>-0.3587</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.397</v>
+        <v>-0.1239</v>
       </c>
       <c r="V3" t="n">
         <v>-2.4554</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.896</v>
+        <v>2.3637</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4583</v>
+        <v>0.0998</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4378</v>
+        <v>2.2639</v>
       </c>
       <c r="G4" t="n">
         <v>0.4443</v>
@@ -766,13 +766,13 @@
         <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1734</v>
+        <v>1.6411</v>
       </c>
       <c r="T4" t="n">
-        <v>1.682</v>
+        <v>1.3235</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4914</v>
+        <v>0.3175</v>
       </c>
       <c r="V4" t="n">
         <v>0.0852</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>M. OLIVA I CAMPABADAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5316</v>
+        <v>1.5037</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4988</v>
+        <v>1.463</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0329</v>
+        <v>0.0406</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1122</v>
+        <v>-1.1062</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1447</v>
+        <v>-1.807</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9676</v>
+        <v>0.7008</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6643</v>
+        <v>-0.0295</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9725</v>
+        <v>-1.2548</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6918</v>
+        <v>1.2253</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5521</v>
+        <v>-1.0767</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8278</v>
+        <v>-0.5522</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2758</v>
+        <v>-0.5245</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3862</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0332</v>
+        <v>0.6412</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1655</v>
+        <v>0.6823</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1988</v>
+        <v>-0.0411</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.741</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.741</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. OLIVA I CAMPABADAL</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9617</v>
+        <v>1.333</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9459</v>
+        <v>1.4988</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0158</v>
+        <v>-0.1658</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1062</v>
+        <v>1.1122</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.807</v>
+        <v>0.1447</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7008</v>
+        <v>0.9676</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0295</v>
+        <v>1.6643</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2548</v>
+        <v>0.9725</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2253</v>
+        <v>0.6918</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0767</v>
+        <v>-0.5521</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5522</v>
+        <v>-0.8278</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5245</v>
+        <v>0.2758</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0993</v>
+        <v>-0.1654</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1652</v>
+        <v>-0.1655</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0659</v>
+        <v>0.0001</v>
       </c>
       <c r="V6" t="n">
-        <v>2.741</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.741</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6563</v>
+        <v>0.2481</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4142</v>
+        <v>-2.7727</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0705</v>
+        <v>3.0208</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0115</v>
@@ -1000,13 +1000,13 @@
         <v>2.1239</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2703</v>
+        <v>-0.1378</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4132</v>
+        <v>0.0547</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1429</v>
+        <v>-0.1925</v>
       </c>
       <c r="V7" t="n">
         <v>2.1698</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0103</v>
+        <v>0.1636</v>
       </c>
       <c r="E8" t="n">
         <v>1.784</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7943</v>
+        <v>-1.6205</v>
       </c>
       <c r="G8" t="n">
         <v>1.9726</v>
@@ -1078,13 +1078,13 @@
         <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3184</v>
+        <v>-1.1446</v>
       </c>
       <c r="T8" t="n">
         <v>-0.7174</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.601</v>
+        <v>-0.4272</v>
       </c>
       <c r="V8" t="n">
         <v>-0.0852</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>J. SOLA ARGEMI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5262</v>
+        <v>-0.85</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5819</v>
+        <v>-0.6214</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0558</v>
+        <v>-0.2286</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1899</v>
+        <v>-2.745</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2554</v>
+        <v>-0.6969</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06560000000000001</v>
+        <v>-2.0481</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.4303</v>
+        <v>-0.8474</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2548</v>
+        <v>0.4072</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1755</v>
+        <v>-1.2546</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2404</v>
+        <v>-1.8977</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-1.1041</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2411</v>
+        <v>-0.7935</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9654</v>
+        <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3363</v>
+        <v>0.3585</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4139</v>
+        <v>0.6202</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0776</v>
+        <v>-0.2617</v>
       </c>
       <c r="V9" t="n">
+        <v>0.5712</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5712</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.2277</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-1.2277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SOLA ARGEMI</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.694</v>
+        <v>-1.5207</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2419</v>
+        <v>-2.5267</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4521</v>
+        <v>1.0061</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.745</v>
+        <v>-1.1899</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6969</v>
+        <v>-1.2554</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0481</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8474</v>
+        <v>-2.4303</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4072</v>
+        <v>-1.2548</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2546</v>
+        <v>-1.1755</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8977</v>
+        <v>1.2404</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1041</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7935</v>
+        <v>1.2411</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9308</v>
+        <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4855</v>
+        <v>-0.3308</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0004</v>
+        <v>-0.3587</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4852</v>
+        <v>0.0279</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5712</v>
+        <v>1.2277</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9016</v>
+        <v>-1.5995</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7459</v>
+        <v>0.8494</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6475</v>
+        <v>-2.4488</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5509</v>
@@ -1312,13 +1312,13 @@
         <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1047</v>
+        <v>0.4067</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3859</v>
+        <v>0.4893</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2813</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2277</v>
@@ -1345,43 +1345,43 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.4825</v>
+        <v>10.7585</v>
       </c>
       <c r="E12" t="n">
-        <v>7.4059</v>
+        <v>7.681900000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>3.076800000000001</v>
+        <v>3.0767</v>
       </c>
       <c r="G12" t="n">
         <v>5.344299999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6918000000000003</v>
+        <v>-0.6918</v>
       </c>
       <c r="I12" t="n">
-        <v>6.036199999999999</v>
+        <v>6.0362</v>
       </c>
       <c r="J12" t="n">
         <v>8.6296</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1416</v>
+        <v>4.141600000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>4.4882</v>
+        <v>4.488199999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-3.2855</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.833299999999999</v>
+        <v>-4.8333</v>
       </c>
       <c r="O12" t="n">
         <v>1.5482</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9654999999999998</v>
+        <v>0.9655</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.5848</v>
@@ -1390,13 +1390,13 @@
         <v>12.5502</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5173</v>
+        <v>1.7931</v>
       </c>
       <c r="T12" t="n">
-        <v>2.0654</v>
+        <v>2.3414</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5482</v>
+        <v>-0.5484000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>2.6557</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4052</v>
+        <v>3.1914</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8353</v>
+        <v>1.7319</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5698</v>
+        <v>1.4594</v>
       </c>
       <c r="G13" t="n">
         <v>1.4949</v>
@@ -1468,13 +1468,13 @@
         <v>1.7377</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5242</v>
+        <v>0.3103</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2201</v>
+        <v>0.1167</v>
       </c>
       <c r="U13" t="n">
-        <v>0.304</v>
+        <v>0.1936</v>
       </c>
       <c r="V13" t="n">
         <v>0.6138</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9214</v>
+        <v>2.6249</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6728</v>
+        <v>0.3625</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2487</v>
+        <v>2.2624</v>
       </c>
       <c r="G14" t="n">
         <v>1.2114</v>
@@ -1546,13 +1546,13 @@
         <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9377</v>
+        <v>0.6412</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4132</v>
+        <v>0.1029</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5245</v>
+        <v>0.5382</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. GONZALEZ CAMEJO</t>
+          <t>S. RODRIGUEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7279</v>
+        <v>-0.0403</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1397</v>
+        <v>-1.3233</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8677</v>
+        <v>1.283</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.6855</v>
+        <v>0.2287</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6623</v>
+        <v>-0.9514</v>
       </c>
       <c r="I15" t="n">
-        <v>-6.3479</v>
+        <v>1.1801</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.6838</v>
+        <v>1.2298</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6286</v>
+        <v>0.0835</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.3124</v>
+        <v>1.1462</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0017</v>
+        <v>-1.0011</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9661999999999999</v>
+        <v>-1.0349</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0355</v>
+        <v>0.0338</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7723</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.0892</v>
+        <v>-2.1239</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3169</v>
+        <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2745</v>
+        <v>0.1171</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7164</v>
+        <v>0.2272</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5581</v>
+        <v>-0.1101</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>5.1964</v>
+        <v>-0.6565</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.741</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ HERNANDEZ</t>
+          <t>G. CAMPOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8361</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6336</v>
+        <v>0.6959</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7975</v>
+        <v>-1.3648</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2287</v>
+        <v>0.923</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9514</v>
+        <v>0.4687</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1801</v>
+        <v>0.4544</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2298</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0835</v>
+        <v>0.1242</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1462</v>
+        <v>0.572</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0011</v>
+        <v>0.2269</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0349</v>
+        <v>0.3445</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0338</v>
+        <v>-0.1176</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1239</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7377</v>
+        <v>0.5792</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6787</v>
+        <v>-0.3723</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5956</v>
+        <v>-0.3721</v>
       </c>
       <c r="V16" t="n">
+        <v>-1.7989</v>
+      </c>
+      <c r="W16" t="n">
         <v>0</v>
       </c>
-      <c r="W16" t="n">
-        <v>-0.6565</v>
-      </c>
       <c r="X16" t="n">
-        <v>0.6565</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. CAMPOS RODRÍGUEZ</t>
+          <t>J. GARCIA CABRERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1075</v>
+        <v>-1.0877</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2822</v>
+        <v>1.4262</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3897</v>
+        <v>-2.5139</v>
       </c>
       <c r="G17" t="n">
-        <v>0.923</v>
+        <v>1.4502</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4687</v>
+        <v>1.4344</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4544</v>
+        <v>0.0158</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6961000000000001</v>
+        <v>2.52</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1242</v>
+        <v>1.9865</v>
       </c>
       <c r="L17" t="n">
-        <v>0.572</v>
+        <v>0.5336</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2269</v>
+        <v>-1.0698</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3445</v>
+        <v>-0.5521</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1176</v>
+        <v>-0.5178</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5792</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R17" t="n">
         <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8108</v>
+        <v>-0.9241</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4139</v>
+        <v>-0.414</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3969</v>
+        <v>-0.51</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.7989</v>
+        <v>-1.2277</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7989</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GARCIA CABRERA</t>
+          <t>E. RAMOS BELASTEGUI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8517</v>
+        <v>-1.5138</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0125</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8642</v>
+        <v>-0.7594</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4502</v>
+        <v>-0.3348</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4344</v>
+        <v>-0.0069</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0158</v>
+        <v>-0.3278</v>
       </c>
       <c r="J18" t="n">
-        <v>2.52</v>
+        <v>0.4525</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9865</v>
+        <v>0.4072</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5336</v>
+        <v>0.0453</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0698</v>
+        <v>-0.7872</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5521</v>
+        <v>-0.4142</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5178</v>
+        <v>-0.3731</v>
       </c>
       <c r="P18" t="n">
         <v>-0.3862</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.688</v>
+        <v>-0.7929</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8277</v>
+        <v>-0.0485</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8603</v>
+        <v>-0.7444</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. RAMOS BELASTEGUI</t>
+          <t>E. GONZALEZ CAMEJO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.26</v>
+        <v>-1.5611</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0647</v>
+        <v>0.726</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1952</v>
+        <v>-2.2872</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3348</v>
+        <v>-3.6855</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0069</v>
+        <v>2.6623</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3278</v>
+        <v>-6.3479</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4525</v>
+        <v>-1.6838</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4072</v>
+        <v>3.6286</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0453</v>
+        <v>-5.3124</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7872</v>
+        <v>-2.0017</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4142</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3731</v>
+        <v>-1.0355</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3862</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1585</v>
+        <v>-3.0892</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7723</v>
+        <v>2.3169</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.539</v>
+        <v>0.4413</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3587</v>
+        <v>0.3027</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1803</v>
+        <v>0.1386</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>5.1964</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0883</v>
+        <v>-3.5999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2336</v>
+        <v>-0.4904</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3219</v>
+        <v>-3.1095</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2009</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4908</v>
+        <v>-0.0208</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9927</v>
+        <v>0.2687</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5019</v>
+        <v>-0.2895</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1851</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.9378</v>
+        <v>-6.4482</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.5546</v>
+        <v>-5.4512</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3832</v>
+        <v>-0.997</v>
       </c>
       <c r="G21" t="n">
         <v>-4.4314</v>
@@ -2092,13 +2092,13 @@
         <v>1.9308</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0278</v>
+        <v>0.4619</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1107</v>
+        <v>-0.0073</v>
       </c>
       <c r="U21" t="n">
-        <v>0.083</v>
+        <v>0.4692</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5133</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.4827</v>
+        <v>-9.1036</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0768</v>
+        <v>-3.0769</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.405900000000001</v>
+        <v>-6.027</v>
       </c>
       <c r="G22" t="n">
         <v>-5.3444</v>
@@ -2152,7 +2152,7 @@
         <v>-1.5481</v>
       </c>
       <c r="M22" t="n">
-        <v>-8.6295</v>
+        <v>-8.629500000000002</v>
       </c>
       <c r="N22" t="n">
         <v>-4.1416</v>
@@ -2170,22 +2170,22 @@
         <v>11.5846</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5171</v>
+        <v>-0.1383000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5482999999999999</v>
+        <v>0.5482000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.0654</v>
+        <v>-0.6864999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.655800000000001</v>
+        <v>-2.6558</v>
       </c>
       <c r="W22" t="n">
         <v>5.639699999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>-8.295400000000001</v>
+        <v>-8.295399999999999</v>
       </c>
     </row>
   </sheetData>
